--- a/exports/CANBK_full_report.xlsx
+++ b/exports/CANBK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>6.83</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.38541666666</v>
+        <v>44582.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>38.35</v>
+        <v>37.55</v>
       </c>
       <c r="I2" t="n">
         <v>37.64864856125773</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>1.86</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>8.06</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44586.55208333334</v>
+        <v>44588.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>38.21</v>
+        <v>41.01</v>
       </c>
       <c r="I3" t="n">
         <v>39.00949571496805</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.76</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>3.12</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>6.79</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="O3" t="n">
         <v>-5.3</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>14.8</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>43.81</v>
+        <v>42.46</v>
       </c>
       <c r="I4" t="n">
         <v>42.5012713825132</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>6.83</v>
+        <v>3.54</v>
       </c>
       <c r="L4" t="n">
         <v>8.75</v>
       </c>
       <c r="M4" t="n">
-        <v>1.23</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4</v>
+        <v>7.35</v>
       </c>
       <c r="O4" t="n">
         <v>9.789999999999999</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44634.55208333334</v>
+        <v>44635.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>38.3</v>
+        <v>38.49</v>
       </c>
       <c r="I5" t="n">
         <v>38.36152397891019</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="L5" t="n">
         <v>3.3</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>8.33</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>42.31</v>
+        <v>40.4</v>
       </c>
       <c r="I6" t="n">
         <v>41.21234423879416</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K6" t="n">
-        <v>9.92</v>
+        <v>4.96</v>
       </c>
       <c r="L6" t="n">
         <v>2.08</v>
       </c>
       <c r="M6" t="n">
-        <v>0.47</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.18</v>
+        <v>3.29</v>
       </c>
       <c r="O6" t="n">
         <v>-1.46</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>34</v>
+        <v>35.59</v>
       </c>
       <c r="I7" t="n">
         <v>35.09897280879238</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K7" t="n">
-        <v>15.84</v>
+        <v>11.91</v>
       </c>
       <c r="L7" t="n">
         <v>5.1</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>10.79</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>35.78</v>
+        <v>33.77</v>
       </c>
       <c r="I8" t="n">
         <v>34.29573452987667</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>0.53</v>
+        <v>-5.11</v>
       </c>
       <c r="L8" t="n">
-        <v>3.18</v>
+        <v>5.51</v>
       </c>
       <c r="M8" t="n">
-        <v>1.31</v>
+        <v>2.63</v>
       </c>
       <c r="N8" t="n">
-        <v>2.08</v>
+        <v>4.97</v>
       </c>
       <c r="O8" t="n">
         <v>6.06</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,25 +1040,25 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>31.67</v>
+        <v>32.41</v>
       </c>
       <c r="I9" t="n">
         <v>32.26296643230101</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>6.22</v>
+        <v>4.03</v>
       </c>
       <c r="L9" t="n">
         <v>3.61</v>
       </c>
       <c r="M9" t="n">
-        <v>1.43</v>
+        <v>2.02</v>
       </c>
       <c r="N9" t="n">
         <v>4.4</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.9</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>40.03</v>
+        <v>38.63</v>
       </c>
       <c r="I10" t="n">
         <v>39.33814413300449</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K10" t="n">
-        <v>23.51</v>
+        <v>19.19</v>
       </c>
       <c r="L10" t="n">
         <v>6.33</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,25 +1178,25 @@
         <v>9.01</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44797.55208333334</v>
+        <v>44798.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>40.4</v>
+        <v>42.03</v>
       </c>
       <c r="I11" t="n">
         <v>41.27738163433576</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.58</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>4.71</v>
+        <v>9.32</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="N11" t="n">
         <v>4.01</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.68</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44826.55208333334</v>
+        <v>44827.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>42.41</v>
+        <v>40.26</v>
       </c>
       <c r="I12" t="n">
         <v>41.953615541102</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9</v>
+        <v>-4.21</v>
       </c>
       <c r="L12" t="n">
         <v>5.12</v>
@@ -1125,7 +1268,7 @@
         <v>3.33</v>
       </c>
       <c r="N12" t="n">
-        <v>3.17</v>
+        <v>6.04</v>
       </c>
       <c r="O12" t="n">
         <v>3.02</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>11.21</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44848.55208333334</v>
+        <v>44851.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>39.47</v>
+        <v>41.1</v>
       </c>
       <c r="I13" t="n">
         <v>39.97603464226061</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K13" t="n">
-        <v>1.96</v>
+        <v>-2.09</v>
       </c>
       <c r="L13" t="n">
         <v>5.59</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>10.57</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44901.55208333334</v>
+        <v>44902.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>56.48</v>
+        <v>55.63</v>
       </c>
       <c r="I14" t="n">
         <v>55.69823681237256</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>51</v>
       </c>
       <c r="K14" t="n">
-        <v>37.42</v>
+        <v>35.35</v>
       </c>
       <c r="L14" t="n">
         <v>5.45</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>6.6</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44924.38541666666</v>
+        <v>44924.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>56.01</v>
+        <v>57.37</v>
       </c>
       <c r="I15" t="n">
         <v>56.2567915242849</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.68</v>
+        <v>-3.13</v>
       </c>
       <c r="L15" t="n">
         <v>5.81</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>8.76</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44942.55208333334</v>
+        <v>44943.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>57.37</v>
+        <v>55.96</v>
       </c>
       <c r="I16" t="n">
         <v>56.05628787667834</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>-2.46</v>
       </c>
       <c r="L16" t="n">
         <v>3.52</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.15</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44986.38541666666</v>
+        <v>44986.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>50.49</v>
+        <v>50.82</v>
       </c>
       <c r="I17" t="n">
         <v>50.54349247769689</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K17" t="n">
-        <v>9.77</v>
+        <v>9.19</v>
       </c>
       <c r="L17" t="n">
         <v>4.18</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>6.01</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44995.55208333334</v>
+        <v>44998.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>52.83</v>
+        <v>52.36</v>
       </c>
       <c r="I18" t="n">
         <v>52.37310035439344</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>3.96</v>
+        <v>3.03</v>
       </c>
       <c r="L18" t="n">
         <v>0.73</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>7.36</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45029.55208333334</v>
+        <v>45033.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>51.34</v>
+        <v>52.28</v>
       </c>
       <c r="I19" t="n">
         <v>51.42818792813216</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>35</v>
       </c>
       <c r="K19" t="n">
-        <v>1.95</v>
+        <v>0.15</v>
       </c>
       <c r="L19" t="n">
         <v>2.6</v>
@@ -1524,7 +1751,7 @@
         <v>1.49</v>
       </c>
       <c r="N19" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="O19" t="n">
         <v>-3.54</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.16</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45051.55208333334</v>
+        <v>45054.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>56.71</v>
+        <v>55.17</v>
       </c>
       <c r="I20" t="n">
         <v>55.18762331193829</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K20" t="n">
-        <v>8.470000000000001</v>
+        <v>5.53</v>
       </c>
       <c r="L20" t="n">
         <v>2.6</v>
@@ -1581,7 +1820,7 @@
         <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="O20" t="n">
         <v>2.28</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>6.13</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45078.55208333334</v>
+        <v>45079.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>54.89</v>
+        <v>55.78</v>
       </c>
       <c r="I21" t="n">
         <v>55.23498203891403</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K21" t="n">
-        <v>0.51</v>
+        <v>-1.11</v>
       </c>
       <c r="L21" t="n">
         <v>3.21</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>4.62</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45090.55208333334</v>
+        <v>45091.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>55.87</v>
+        <v>54.05</v>
       </c>
       <c r="I22" t="n">
         <v>54.09425428357991</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K22" t="n">
-        <v>0.16</v>
+        <v>-3.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.86</v>
+        <v>3.85</v>
       </c>
       <c r="M22" t="n">
-        <v>-0</v>
+        <v>3.53</v>
       </c>
       <c r="N22" t="n">
-        <v>0.84</v>
+        <v>3.53</v>
       </c>
       <c r="O22" t="n">
         <v>1.18</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>4.03</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45107.55208333334</v>
+        <v>45110.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>53.44</v>
+        <v>55.35</v>
       </c>
       <c r="I23" t="n">
         <v>54.11008048950325</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K23" t="n">
-        <v>1.13</v>
+        <v>-2.41</v>
       </c>
       <c r="L23" t="n">
-        <v>1.46</v>
+        <v>2.59</v>
       </c>
       <c r="M23" t="n">
         <v>0.63</v>
       </c>
       <c r="N23" t="n">
-        <v>2.3</v>
+        <v>5.78</v>
       </c>
       <c r="O23" t="n">
         <v>-3.53</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.06</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45140.38541666666</v>
+        <v>45140.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>58.39</v>
+        <v>58.11</v>
       </c>
       <c r="I24" t="n">
         <v>58.16222344409726</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>30</v>
+        <v>30.16666666666667</v>
       </c>
       <c r="K24" t="n">
-        <v>5.49</v>
+        <v>4.99</v>
       </c>
       <c r="L24" t="n">
         <v>3.29</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>5.76</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45170.55208333334</v>
+        <v>45173.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>58.3</v>
+        <v>59.57</v>
       </c>
       <c r="I25" t="n">
         <v>59.19433847645649</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>30</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.33</v>
+        <v>-2.51</v>
       </c>
       <c r="L25" t="n">
         <v>4.1</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.56</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45222.38541666666</v>
+        <v>45222.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>64.79000000000001</v>
+        <v>63.39</v>
       </c>
       <c r="I26" t="n">
         <v>64.47177484273918</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K26" t="n">
-        <v>8.76</v>
+        <v>6.41</v>
       </c>
       <c r="L26" t="n">
         <v>2.37</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>7.24</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45225.55208333334</v>
+        <v>45226.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>64.38</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="I27" t="n">
         <v>66.19324161194325</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.56</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>2.89</v>
+        <v>9.59</v>
       </c>
       <c r="M27" t="n">
         <v>1.4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.08</v>
+        <v>5.87</v>
       </c>
       <c r="O27" t="n">
         <v>-3.9</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.32</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45253.55208333334</v>
+        <v>45254.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>70.64</v>
+        <v>69.98</v>
       </c>
       <c r="I28" t="n">
         <v>70.15440143352912</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K28" t="n">
-        <v>3.14</v>
+        <v>2.18</v>
       </c>
       <c r="L28" t="n">
         <v>5.81</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>4.93</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45260.55208333334</v>
+        <v>45261.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>72.59999999999999</v>
+        <v>73.53</v>
       </c>
       <c r="I29" t="n">
         <v>72.77201011527563</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.74</v>
+        <v>-5.07</v>
       </c>
       <c r="L29" t="n">
-        <v>4.27</v>
+        <v>7.62</v>
       </c>
       <c r="M29" t="n">
         <v>0.85</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>4.17</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>79.52</v>
+        <v>76.48</v>
       </c>
       <c r="I30" t="n">
         <v>77.48557126242068</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>8.15</v>
+        <v>4.01</v>
       </c>
       <c r="L30" t="n">
         <v>1.14</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>8.18</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45293.55208333334</v>
+        <v>45294.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>80.12</v>
+        <v>83.3</v>
       </c>
       <c r="I31" t="n">
         <v>80.84006436503228</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.76</v>
+        <v>-8.92</v>
       </c>
       <c r="L31" t="n">
-        <v>6.16</v>
+        <v>9.17</v>
       </c>
       <c r="M31" t="n">
         <v>2.11</v>
       </c>
       <c r="N31" t="n">
-        <v>1.81</v>
+        <v>3.44</v>
       </c>
       <c r="O31" t="n">
         <v>-4.77</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.46</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>102.79</v>
+        <v>99.19</v>
       </c>
       <c r="I32" t="n">
         <v>102.7189682262073</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>69.16666666666667</v>
+        <v>70</v>
       </c>
       <c r="K32" t="n">
-        <v>23.4</v>
+        <v>19.08</v>
       </c>
       <c r="L32" t="n">
         <v>4.54</v>
@@ -2265,7 +2648,7 @@
         <v>1.94</v>
       </c>
       <c r="N32" t="n">
-        <v>4.75</v>
+        <v>5.64</v>
       </c>
       <c r="O32" t="n">
         <v>3.44</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>9.52</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45378.55208333334</v>
+        <v>45379.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>102.64</v>
+        <v>106.43</v>
       </c>
       <c r="I33" t="n">
         <v>105.9571873518962</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.48</v>
+        <v>-7.3</v>
       </c>
       <c r="L33" t="n">
-        <v>5.8</v>
+        <v>7.35</v>
       </c>
       <c r="M33" t="n">
         <v>1.31</v>
       </c>
       <c r="N33" t="n">
-        <v>2.32</v>
+        <v>3.15</v>
       </c>
       <c r="O33" t="n">
         <v>-5.64</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.31</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45397.55208333334</v>
+        <v>45398.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>107.93</v>
+        <v>106.29</v>
       </c>
       <c r="I34" t="n">
         <v>106.8374485093648</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K34" t="n">
-        <v>1.41</v>
+        <v>-0.13</v>
       </c>
       <c r="L34" t="n">
         <v>3.07</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>6.06</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45406.55208333334</v>
+        <v>45407.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>108.58</v>
+        <v>111.85</v>
       </c>
       <c r="I35" t="n">
         <v>110.0361234285296</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.15</v>
+        <v>-5.23</v>
       </c>
       <c r="L35" t="n">
-        <v>3.69</v>
+        <v>5.4</v>
       </c>
       <c r="M35" t="n">
         <v>1.05</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>6.75</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45415.55208333334</v>
+        <v>45418.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>114</v>
+        <v>107.74</v>
       </c>
       <c r="I36" t="n">
         <v>109.3376333382459</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K36" t="n">
-        <v>1.92</v>
+        <v>-3.67</v>
       </c>
       <c r="L36" t="n">
-        <v>3.25</v>
+        <v>4.39</v>
       </c>
       <c r="M36" t="n">
         <v>0.17</v>
       </c>
       <c r="N36" t="n">
-        <v>0.45</v>
+        <v>5.57</v>
       </c>
       <c r="O36" t="n">
         <v>3.22</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>9.16</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45426.55208333334</v>
+        <v>45427.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>103.35</v>
+        <v>107.97</v>
       </c>
       <c r="I37" t="n">
         <v>107.5009662145898</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K37" t="n">
-        <v>4.07</v>
+        <v>-0.21</v>
       </c>
       <c r="L37" t="n">
         <v>6.33</v>
       </c>
       <c r="M37" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="N37" t="n">
-        <v>3.27</v>
+        <v>4.7</v>
       </c>
       <c r="O37" t="n">
         <v>-5.57</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>9.83</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>117.46</v>
+        <v>99.7</v>
       </c>
       <c r="I38" t="n">
         <v>108.5477659660511</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K38" t="n">
-        <v>8.789999999999999</v>
+        <v>-7.66</v>
       </c>
       <c r="L38" t="n">
-        <v>6.02</v>
+        <v>19.52</v>
       </c>
       <c r="M38" t="n">
-        <v>0.09</v>
+        <v>0.88</v>
       </c>
       <c r="N38" t="n">
-        <v>4.41</v>
+        <v>14.36</v>
       </c>
       <c r="O38" t="n">
         <v>4.7</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>18.56</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45525.55208333334</v>
+        <v>45526.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>104.43</v>
+        <v>104.74</v>
       </c>
       <c r="I39" t="n">
         <v>104.4317215799751</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>78.16666666666667</v>
+        <v>79</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.74</v>
+        <v>-5.06</v>
       </c>
       <c r="L39" t="n">
         <v>16.78</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>4.22</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45540.55208333334</v>
+        <v>45541.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>101.17</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="I40" t="n">
         <v>100.9855293306005</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.41</v>
+        <v>-7.32</v>
       </c>
       <c r="L40" t="n">
-        <v>3.86</v>
+        <v>7.59</v>
       </c>
       <c r="M40" t="n">
         <v>3.03</v>
       </c>
       <c r="N40" t="n">
-        <v>2.57</v>
+        <v>4.37</v>
       </c>
       <c r="O40" t="n">
         <v>0.52</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>7.03</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45555.55208333334</v>
+        <v>45558.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>98.31999999999999</v>
+        <v>101.75</v>
       </c>
       <c r="I41" t="n">
         <v>100.500426230344</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.29</v>
+        <v>-4.82</v>
       </c>
       <c r="L41" t="n">
-        <v>4.15</v>
+        <v>5.37</v>
       </c>
       <c r="M41" t="n">
         <v>0.76</v>
       </c>
       <c r="N41" t="n">
-        <v>2.36</v>
+        <v>3.9</v>
       </c>
       <c r="O41" t="n">
         <v>-4.37</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>6.73</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>100.71</v>
+        <v>97</v>
       </c>
       <c r="I42" t="n">
         <v>99.39466676022788</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.02</v>
+        <v>-4.67</v>
       </c>
       <c r="L42" t="n">
-        <v>3.51</v>
+        <v>4.88</v>
       </c>
       <c r="M42" t="n">
         <v>2.31</v>
       </c>
       <c r="N42" t="n">
-        <v>2.45</v>
+        <v>3.68</v>
       </c>
       <c r="O42" t="n">
         <v>3.9</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>9.51</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45593.38541666666</v>
+        <v>45593.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>92.03</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="I43" t="n">
         <v>94.19895478168242</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>5.12</v>
+        <v>2.39</v>
       </c>
       <c r="L43" t="n">
         <v>5.07</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>9.16</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45609.38541666666</v>
+        <v>45609.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>93.27</v>
+        <v>92.48</v>
       </c>
       <c r="I44" t="n">
         <v>92.87853938063517</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.49</v>
+        <v>-2.32</v>
       </c>
       <c r="L44" t="n">
-        <v>3.16</v>
+        <v>3.72</v>
       </c>
       <c r="M44" t="n">
         <v>0.43</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>6.3</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45622.55208333334</v>
+        <v>45623.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>95.04000000000001</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="I45" t="n">
         <v>95.38551050251903</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.77</v>
+        <v>-3.46</v>
       </c>
       <c r="L45" t="n">
-        <v>3.65</v>
+        <v>3.78</v>
       </c>
       <c r="M45" t="n">
         <v>3.1</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>6.86</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>98.20999999999999</v>
+        <v>96.52</v>
       </c>
       <c r="I46" t="n">
         <v>97.8283045076283</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K46" t="n">
-        <v>2.64</v>
+        <v>0.88</v>
       </c>
       <c r="L46" t="n">
         <v>1.59</v>
       </c>
       <c r="M46" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="N46" t="n">
         <v>1.98</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>5.1</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45671.55208333334</v>
+        <v>45672.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>87.48</v>
+        <v>88.78</v>
       </c>
       <c r="I47" t="n">
         <v>88.42830048651332</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K47" t="n">
-        <v>9.369999999999999</v>
+        <v>8.02</v>
       </c>
       <c r="L47" t="n">
         <v>1.67</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>7.02</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45684.38541666666</v>
+        <v>45684.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>90.84</v>
+        <v>86.03</v>
       </c>
       <c r="I48" t="n">
         <v>89.23902178964747</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>2.32</v>
+        <v>-3.1</v>
       </c>
       <c r="L48" t="n">
-        <v>1.4</v>
+        <v>4.33</v>
       </c>
       <c r="M48" t="n">
         <v>0.71</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>10.38</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45721.55208333334</v>
+        <v>45722.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>79.5</v>
+        <v>80.28</v>
       </c>
       <c r="I49" t="n">
         <v>80.16727372696877</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>37</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K49" t="n">
-        <v>7.59</v>
+        <v>6.68</v>
       </c>
       <c r="L49" t="n">
         <v>6.02</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>6.22</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>84.68000000000001</v>
+        <v>80.39</v>
       </c>
       <c r="I50" t="n">
         <v>82.75913671568067</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K50" t="n">
-        <v>5.48</v>
+        <v>0.14</v>
       </c>
       <c r="L50" t="n">
         <v>5.24</v>
       </c>
       <c r="M50" t="n">
-        <v>1.17</v>
+        <v>7.63</v>
       </c>
       <c r="N50" t="n">
         <v>3.86</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>8.66</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45762.55208333334</v>
+        <v>45763.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>86.76000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I51" t="n">
         <v>87.35056933426878</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K51" t="n">
-        <v>-7.92</v>
+        <v>-10.21</v>
       </c>
       <c r="L51" t="n">
-        <v>8.050000000000001</v>
+        <v>10.37</v>
       </c>
       <c r="M51" t="n">
         <v>2.77</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.92</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45782.55208333334</v>
+        <v>45783.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>90.98</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="I52" t="n">
         <v>88.99524941987779</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>2.69</v>
+        <v>-0.16</v>
       </c>
       <c r="L52" t="n">
         <v>2.43</v>
@@ -3405,7 +4028,7 @@
         <v>0.1</v>
       </c>
       <c r="N52" t="n">
-        <v>3.01</v>
+        <v>5.41</v>
       </c>
       <c r="O52" t="n">
         <v>2.01</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>7.38</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45786.55208333334</v>
+        <v>45789.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>91.43000000000001</v>
+        <v>93.48999999999999</v>
       </c>
       <c r="I53" t="n">
         <v>92.33392999498059</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.36</v>
+        <v>-5.69</v>
       </c>
       <c r="L53" t="n">
-        <v>4</v>
+        <v>7.18</v>
       </c>
       <c r="M53" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.72</v>
       </c>
       <c r="N53" t="n">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="O53" t="n">
         <v>-5.41</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.85</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45825.55208333334</v>
+        <v>45826.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>105.52</v>
+        <v>105.33</v>
       </c>
       <c r="I54" t="n">
         <v>105.3330961581173</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K54" t="n">
-        <v>12.87</v>
+        <v>12.66</v>
       </c>
       <c r="L54" t="n">
         <v>0.18</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>4.98</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>104.36</v>
+        <v>107.37</v>
       </c>
       <c r="I55" t="n">
         <v>106.8978797594764</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K55" t="n">
-        <v>0.92</v>
+        <v>-1.94</v>
       </c>
       <c r="L55" t="n">
-        <v>0.96</v>
+        <v>2.42</v>
       </c>
       <c r="M55" t="n">
-        <v>0.21</v>
+        <v>1.67</v>
       </c>
       <c r="N55" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="O55" t="n">
         <v>-0.72</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.72</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45859.38541666666</v>
+        <v>45859.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>110.89</v>
+        <v>108.47</v>
       </c>
       <c r="I56" t="n">
         <v>108.9047312393191</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K56" t="n">
-        <v>3.28</v>
+        <v>1.02</v>
       </c>
       <c r="L56" t="n">
         <v>1.99</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>5.42</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45862.38541666666</v>
+        <v>45862.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>104.13</v>
+        <v>110.24</v>
       </c>
       <c r="I57" t="n">
         <v>109.2979994055494</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K57" t="n">
-        <v>4</v>
+        <v>-1.63</v>
       </c>
       <c r="L57" t="n">
         <v>2.33</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45894.55208333334</v>
+        <v>45895.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>105.49</v>
+        <v>103.1</v>
       </c>
       <c r="I58" t="n">
         <v>105.1297810746955</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>32</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.31</v>
+        <v>-6.48</v>
       </c>
       <c r="L58" t="n">
         <v>7.14</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>4.99</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45903.38541666666</v>
+        <v>45903.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>104.28</v>
+        <v>104.84</v>
       </c>
       <c r="I59" t="n">
         <v>104.3122725390448</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.14</v>
+        <v>-1.69</v>
       </c>
       <c r="L59" t="n">
         <v>2.41</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>3.68</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45993.55208333334</v>
+        <v>45994.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>147.32</v>
+        <v>141.11</v>
       </c>
       <c r="I60" t="n">
         <v>141.5394670459225</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>90</v>
+        <v>90.83333333333333</v>
       </c>
       <c r="K60" t="n">
-        <v>40.52</v>
+        <v>34.6</v>
       </c>
       <c r="L60" t="n">
         <v>2.48</v>
@@ -3861,7 +4580,7 @@
         <v>1.05</v>
       </c>
       <c r="N60" t="n">
-        <v>2.58</v>
+        <v>3.86</v>
       </c>
       <c r="O60" t="n">
         <v>2.01</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.96</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46008.55208333334</v>
+        <v>46009.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>145.34</v>
+        <v>145.72</v>
       </c>
       <c r="I61" t="n">
         <v>145.6484369673817</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K61" t="n">
-        <v>-3</v>
+        <v>-3.27</v>
       </c>
       <c r="L61" t="n">
         <v>4.93</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>4.87</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46051.55208333334</v>
+        <v>46052.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>145.88</v>
+        <v>143.11</v>
       </c>
       <c r="I62" t="n">
         <v>144.8535045451528</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K62" t="n">
-        <v>0.11</v>
+        <v>-1.79</v>
       </c>
       <c r="L62" t="n">
-        <v>2.37</v>
+        <v>2.59</v>
       </c>
       <c r="M62" t="n">
         <v>0.52</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>8.15</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46069.55208333334</v>
+        <v>46070.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>141.43</v>
+        <v>144.58</v>
       </c>
       <c r="I63" t="n">
         <v>144.5459744408689</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K63" t="n">
-        <v>1.17</v>
+        <v>-1.03</v>
       </c>
       <c r="L63" t="n">
         <v>6.54</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>7.23</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>148.98</v>
+        <v>142.45</v>
       </c>
       <c r="I64" t="n">
         <v>146.2473873681562</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K64" t="n">
-        <v>3.04</v>
+        <v>-1.47</v>
       </c>
       <c r="L64" t="n">
         <v>3.04</v>
@@ -4089,7 +4856,7 @@
         <v>4.6</v>
       </c>
       <c r="N64" t="n">
-        <v>2.32</v>
+        <v>4.55</v>
       </c>
       <c r="O64" t="n">
         <v>2.19</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>8.24</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>125.27</v>
+        <v>133.21</v>
       </c>
       <c r="I65" t="n">
         <v>130.5634015211444</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K65" t="n">
-        <v>12.06</v>
+        <v>6.49</v>
       </c>
       <c r="L65" t="n">
         <v>2.96</v>
       </c>
       <c r="M65" t="n">
-        <v>3.42</v>
+        <v>5.09</v>
       </c>
       <c r="N65" t="n">
-        <v>3.29</v>
+        <v>7.66</v>
       </c>
       <c r="O65" t="n">
         <v>-4.55</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>9.41</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46139.55208333334</v>
+        <v>46140.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>136.06</v>
+        <v>132.34</v>
       </c>
       <c r="I66" t="n">
         <v>134.1515846327503</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K66" t="n">
-        <v>2.14</v>
+        <v>-0.65</v>
       </c>
       <c r="L66" t="n">
         <v>2.18</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>6.39</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46167.38541666666</v>
+        <v>46167.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>128.3</v>
+        <v>129.81</v>
       </c>
       <c r="I67" t="n">
         <v>128.9365670939206</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K67" t="n">
-        <v>3.05</v>
+        <v>1.91</v>
       </c>
       <c r="L67" t="n">
         <v>2.05</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,25 +5111,25 @@
         <v>6.07</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46174.55208333334</v>
+        <v>46175.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>124.01</v>
+        <v>123.28</v>
       </c>
       <c r="I68" t="n">
         <v>123.7045132437888</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K68" t="n">
-        <v>-4.47</v>
+        <v>-5.03</v>
       </c>
       <c r="L68" t="n">
-        <v>4.91</v>
+        <v>6.41</v>
       </c>
       <c r="M68" t="n">
-        <v>0.23</v>
+        <v>0.86</v>
       </c>
       <c r="N68" t="n">
         <v>2.77</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>5.21</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46177.55208333334</v>
+        <v>46178.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>128.95</v>
+        <v>130.57</v>
       </c>
       <c r="I69" t="n">
         <v>129.7057752746752</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K69" t="n">
-        <v>-4.6</v>
+        <v>-5.91</v>
       </c>
       <c r="L69" t="n">
-        <v>4.79</v>
+        <v>7.08</v>
       </c>
       <c r="M69" t="n">
         <v>0.1</v>
       </c>
       <c r="N69" t="n">
-        <v>1.69</v>
+        <v>2.17</v>
       </c>
       <c r="O69" t="n">
         <v>0.9399999999999999</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>5.83</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46198.55208333334</v>
+        <v>46202.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>129.28</v>
+        <v>125.93</v>
       </c>
       <c r="I70" t="n">
         <v>128.7281621221485</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.99</v>
+        <v>-3.55</v>
       </c>
       <c r="L70" t="n">
-        <v>3.17</v>
+        <v>3.68</v>
       </c>
       <c r="M70" t="n">
         <v>0.93</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>6.32</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46212.55208333334</v>
+        <v>46213.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>125.25</v>
+        <v>129.7</v>
       </c>
       <c r="I71" t="n">
         <v>128.7608303443268</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K71" t="n">
-        <v>0.54</v>
+        <v>-2.99</v>
       </c>
       <c r="L71" t="n">
-        <v>2.91</v>
+        <v>4.41</v>
       </c>
       <c r="M71" t="n">
         <v>1.89</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>6.73</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46262.55208333334</v>
+        <v>46265.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>128.04</v>
+        <v>126.38</v>
       </c>
       <c r="I72" t="n">
         <v>126.974735408301</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K72" t="n">
-        <v>-1.28</v>
+        <v>-2.56</v>
       </c>
       <c r="L72" t="n">
         <v>5.17</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>3.91</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46308.55208333334</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>120.15</v>
+        <v>123.87</v>
       </c>
       <c r="I73" t="n">
         <v>122.4711606228652</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K73" t="n">
-        <v>4.93</v>
+        <v>1.99</v>
       </c>
       <c r="L73" t="n">
         <v>1.83</v>
@@ -4602,7 +5477,7 @@
         <v>1.02</v>
       </c>
       <c r="N73" t="n">
-        <v>2.52</v>
+        <v>3.58</v>
       </c>
       <c r="O73" t="n">
         <v>-1.36</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>6.13</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46310.38541666666</v>
+        <v>46310.55208333334</v>
       </c>
       <c r="H74" t="n">
-        <v>118.16</v>
+        <v>117.25</v>
       </c>
       <c r="I74" t="n">
         <v>117.8606829991418</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K74" t="n">
-        <v>-4.61</v>
+        <v>-5.34</v>
       </c>
       <c r="L74" t="n">
         <v>5.78</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4719,6 +5618,12 @@
       <c r="Q75" t="n">
         <v>15</v>
       </c>
+      <c r="R75" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6821,7 +7726,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.5</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="6">
@@ -6831,7 +7736,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.2</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="7">
@@ -6841,7 +7746,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="8">
@@ -6851,7 +7756,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -6861,7 +7766,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -6871,7 +7776,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43.1</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="11">
@@ -6881,7 +7786,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12">
@@ -6891,7 +7796,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -6901,7 +7806,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>78.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -6911,7 +7816,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.51</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="15">
@@ -6921,7 +7826,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.63</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="16">
@@ -6931,7 +7836,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.34</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="17">
@@ -6941,7 +7846,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>40.52</v>
+        <v>35.35</v>
       </c>
     </row>
     <row r="18">
@@ -6951,7 +7856,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>64.40000000000001</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19">
@@ -6961,7 +7866,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.94</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="20">
@@ -6971,7 +7876,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.51</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="21">
@@ -6981,7 +7886,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.78</v>
+        <v>19.52</v>
       </c>
     </row>
     <row r="22">
@@ -6991,7 +7896,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -7001,7 +7906,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -7011,7 +7916,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="25">
@@ -7021,7 +7926,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.78</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="26">
@@ -7031,7 +7936,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.38</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="27">
@@ -7041,7 +7946,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.06</v>
+        <v>14.36</v>
       </c>
     </row>
     <row r="28">
@@ -7051,7 +7956,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29">
